--- a/academias/Inglés - Estadisticos 20211.xlsx
+++ b/academias/Inglés - Estadisticos 20211.xlsx
@@ -591,25 +591,25 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>80.56</v>
       </c>
       <c r="H2">
-        <v>44.44</v>
+        <v>19.44</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>44.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -626,25 +626,25 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>25.64</v>
+        <v>15.38</v>
       </c>
       <c r="I3">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>25.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -661,25 +661,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H4">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I4">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -696,25 +696,25 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H5">
-        <v>30.56</v>
+        <v>22.22</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -731,25 +731,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>59.38</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>40.63</v>
+        <v>12.5</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>40.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -766,25 +766,25 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H7">
-        <v>40</v>
+        <v>31.43</v>
       </c>
       <c r="I7">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -801,25 +801,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>71.43000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H8">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
       <c r="I8">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -836,25 +836,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="I9">
         <v>6.8</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1268,13 +1268,13 @@
         <v>13.64</v>
       </c>
       <c r="I21">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1303,13 +1303,13 @@
         <v>15.79</v>
       </c>
       <c r="I22">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1571,25 +1571,25 @@
         <v>40</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G30">
-        <v>67.5</v>
+        <v>82.5</v>
       </c>
       <c r="H30">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
       <c r="I30">
         <v>6.3</v>
       </c>
       <c r="J30">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1606,25 +1606,25 @@
         <v>44</v>
       </c>
       <c r="E31">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>70.45</v>
+        <v>77.27</v>
       </c>
       <c r="H31">
-        <v>29.55</v>
+        <v>22.73</v>
       </c>
       <c r="I31">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J31">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>29.55</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1641,25 +1641,25 @@
         <v>43</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G32">
-        <v>69.77</v>
+        <v>83.72</v>
       </c>
       <c r="H32">
-        <v>30.23</v>
+        <v>16.28</v>
       </c>
       <c r="I32">
+        <v>6.8</v>
+      </c>
+      <c r="J32">
         <v>7</v>
       </c>
-      <c r="J32">
-        <v>13</v>
-      </c>
       <c r="K32">
-        <v>30.23</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1676,25 +1676,25 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H33">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
       <c r="I33">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1711,25 +1711,25 @@
         <v>34</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>44.12</v>
+        <v>79.41</v>
       </c>
       <c r="H34">
-        <v>55.88</v>
+        <v>20.59</v>
       </c>
       <c r="I34">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="J34">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>55.88</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1795,22 +1795,25 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.56</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>19.44</v>
+      </c>
+      <c r="I2">
+        <v>7.4</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1827,22 +1830,25 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>15.38</v>
+      </c>
+      <c r="I3">
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1859,22 +1865,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>28</v>
+      </c>
+      <c r="I4">
+        <v>6.7</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1891,22 +1900,25 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I5">
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1923,22 +1935,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I6">
+        <v>7.8</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1955,22 +1970,25 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>31.43</v>
+      </c>
+      <c r="I7">
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1987,22 +2005,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>21.43</v>
+      </c>
+      <c r="I8">
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2019,22 +2040,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>66.67</v>
+      </c>
+      <c r="I9">
+        <v>7.9</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2051,22 +2075,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>54.84</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>45.16</v>
+      </c>
+      <c r="I10">
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2083,22 +2110,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>47.62</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>52.38</v>
+      </c>
+      <c r="I11">
+        <v>9.199999999999999</v>
       </c>
       <c r="J11">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>52.38</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2147,22 +2177,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F13">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>47.62</v>
       </c>
       <c r="H13">
-        <v>100</v>
+        <v>52.38</v>
+      </c>
+      <c r="I13">
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2403,22 +2436,25 @@
         <v>22</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H21">
-        <v>100</v>
+        <v>18.18</v>
+      </c>
+      <c r="I21">
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2435,22 +2471,25 @@
         <v>38</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H22">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I22">
+        <v>7.6</v>
       </c>
       <c r="J22">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2691,22 +2730,25 @@
         <v>40</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F30">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>17.5</v>
+      </c>
+      <c r="I30">
+        <v>6.2</v>
       </c>
       <c r="J30">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2723,22 +2765,25 @@
         <v>44</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F31">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>77.27</v>
       </c>
       <c r="H31">
-        <v>100</v>
+        <v>22.73</v>
+      </c>
+      <c r="I31">
+        <v>6.9</v>
       </c>
       <c r="J31">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2755,22 +2800,25 @@
         <v>43</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F32">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H32">
-        <v>100</v>
+        <v>18.6</v>
+      </c>
+      <c r="I32">
+        <v>6.7</v>
       </c>
       <c r="J32">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2787,22 +2835,25 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F33">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="H33">
-        <v>100</v>
+        <v>38.1</v>
+      </c>
+      <c r="I33">
+        <v>6.7</v>
       </c>
       <c r="J33">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2819,22 +2870,25 @@
         <v>34</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F34">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>55.88</v>
       </c>
       <c r="H34">
-        <v>100</v>
+        <v>44.12</v>
+      </c>
+      <c r="I34">
+        <v>8.6</v>
       </c>
       <c r="J34">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>44.12</v>
       </c>
     </row>
   </sheetData>
@@ -2900,25 +2954,25 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>55.56</v>
+        <v>80.56</v>
       </c>
       <c r="H2">
-        <v>44.44</v>
+        <v>19.44</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>44.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2935,25 +2989,25 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G3">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>25.64</v>
+        <v>15.38</v>
       </c>
       <c r="I3">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>25.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2970,25 +3024,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H4">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I4">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3005,25 +3059,25 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G5">
-        <v>69.44</v>
+        <v>77.78</v>
       </c>
       <c r="H5">
-        <v>30.56</v>
+        <v>22.22</v>
       </c>
       <c r="I5">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>30.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -3040,25 +3094,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G6">
-        <v>59.38</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>40.63</v>
+        <v>12.5</v>
       </c>
       <c r="I6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>40.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -3075,25 +3129,25 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="H7">
-        <v>40</v>
+        <v>31.43</v>
       </c>
       <c r="I7">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -3110,25 +3164,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G8">
-        <v>71.43000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H8">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
       <c r="I8">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>28.57</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3145,25 +3199,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H9">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="I9">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3192,7 +3246,7 @@
         <v>22.58</v>
       </c>
       <c r="I10">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -3215,19 +3269,19 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>47.62</v>
+        <v>57.14</v>
       </c>
       <c r="H11">
-        <v>52.38</v>
+        <v>42.86</v>
       </c>
       <c r="I11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3285,19 +3339,19 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H13">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
       <c r="I13">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -3565,25 +3619,25 @@
         <v>22</v>
       </c>
       <c r="E21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>86.36</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H21">
-        <v>13.64</v>
+        <v>18.18</v>
       </c>
       <c r="I21">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -3600,25 +3654,25 @@
         <v>38</v>
       </c>
       <c r="E22">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>84.20999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="H22">
-        <v>15.79</v>
+        <v>21.05</v>
       </c>
       <c r="I22">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -3880,25 +3934,25 @@
         <v>40</v>
       </c>
       <c r="E30">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G30">
-        <v>67.5</v>
+        <v>82.5</v>
       </c>
       <c r="H30">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
       <c r="I30">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J30">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3915,25 +3969,25 @@
         <v>44</v>
       </c>
       <c r="E31">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>70.45</v>
+        <v>77.27</v>
       </c>
       <c r="H31">
-        <v>29.55</v>
+        <v>22.73</v>
       </c>
       <c r="I31">
         <v>7.1</v>
       </c>
       <c r="J31">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>29.55</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -3950,25 +4004,25 @@
         <v>43</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F32">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G32">
-        <v>69.77</v>
+        <v>83.72</v>
       </c>
       <c r="H32">
-        <v>30.23</v>
+        <v>16.28</v>
       </c>
       <c r="I32">
+        <v>6.9</v>
+      </c>
+      <c r="J32">
         <v>7</v>
       </c>
-      <c r="J32">
-        <v>13</v>
-      </c>
       <c r="K32">
-        <v>30.23</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -3985,25 +4039,25 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H33">
-        <v>42.86</v>
+        <v>38.1</v>
       </c>
       <c r="I33">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K33">
-        <v>38.1</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4020,25 +4074,25 @@
         <v>34</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F34">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G34">
-        <v>44.12</v>
+        <v>79.41</v>
       </c>
       <c r="H34">
-        <v>55.88</v>
+        <v>20.59</v>
       </c>
       <c r="I34">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="J34">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>55.88</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20211.xlsx
+++ b/academias/Inglés - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -184,6 +184,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -236,8 +240,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -538,42 +544,45 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -596,19 +605,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>80.56</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>19.44</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.8</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -631,19 +640,19 @@
       <c r="F3">
         <v>6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>84.62</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>15.38</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -666,19 +675,19 @@
       <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>72</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>28</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>7</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -701,19 +710,19 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>77.78</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>22.22</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -736,19 +745,19 @@
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>87.5</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12.5</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8.1</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -771,19 +780,19 @@
       <c r="F7">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>68.56999999999999</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>31.43</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>6.9</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -806,19 +815,19 @@
       <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>78.56999999999999</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>21.43</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>21.43</v>
       </c>
     </row>
@@ -841,19 +850,19 @@
       <c r="F9">
         <v>11</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>66.67</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>33.33</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.8</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>12.12</v>
       </c>
     </row>
@@ -876,19 +885,19 @@
       <c r="F10">
         <v>7</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>77.42</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>22.58</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.7</v>
       </c>
       <c r="J10">
         <v>3</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>9.68</v>
       </c>
     </row>
@@ -911,19 +920,19 @@
       <c r="F11">
         <v>11</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>47.62</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>52.38</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.2</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>4.76</v>
       </c>
     </row>
@@ -946,19 +955,19 @@
       <c r="F12">
         <v>6</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>82.86</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>17.14</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -981,19 +990,19 @@
       <c r="F13">
         <v>9</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>57.14</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>42.86</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>6.9</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>14.29</v>
       </c>
     </row>
@@ -1016,19 +1025,19 @@
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>96.77</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>3.23</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8.5</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1051,19 +1060,19 @@
       <c r="F15">
         <v>12</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>68.42</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>31.58</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>9.1</v>
       </c>
       <c r="J15">
         <v>12</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>31.58</v>
       </c>
     </row>
@@ -1086,19 +1095,19 @@
       <c r="F16">
         <v>6</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>82.86</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>17.14</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J16">
         <v>6</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>17.14</v>
       </c>
     </row>
@@ -1121,19 +1130,19 @@
       <c r="F17">
         <v>2</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>91.3</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>8.699999999999999</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>9.5</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -1156,19 +1165,19 @@
       <c r="F18">
         <v>16</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>50</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>50</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J18">
         <v>16</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>50</v>
       </c>
     </row>
@@ -1191,19 +1200,19 @@
       <c r="F19">
         <v>6</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>82.34999999999999</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>17.65</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>9.6</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>17.65</v>
       </c>
     </row>
@@ -1226,19 +1235,19 @@
       <c r="F20">
         <v>10</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>69.7</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>30.3</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>9</v>
       </c>
       <c r="J20">
         <v>10</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>30.3</v>
       </c>
     </row>
@@ -1261,19 +1270,19 @@
       <c r="F21">
         <v>3</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>86.36</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>13.64</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>7.9</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1296,19 +1305,19 @@
       <c r="F22">
         <v>6</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>84.20999999999999</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>15.79</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7.7</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1331,19 +1340,19 @@
       <c r="F23">
         <v>7</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>80</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>20</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>8.6</v>
       </c>
       <c r="J23">
         <v>7</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>20</v>
       </c>
     </row>
@@ -1366,19 +1375,19 @@
       <c r="F24">
         <v>9</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>70.97</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>29.03</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>6.6</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1401,19 +1410,19 @@
       <c r="F25">
         <v>7</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>80.56</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>19.44</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>7.5</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1436,19 +1445,19 @@
       <c r="F26">
         <v>9</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>79.06999999999999</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>20.93</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>7.5</v>
       </c>
       <c r="J26">
         <v>2</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>4.65</v>
       </c>
     </row>
@@ -1471,19 +1480,19 @@
       <c r="F27">
         <v>5</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>88.37</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>11.63</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>7.1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1506,19 +1515,19 @@
       <c r="F28">
         <v>3</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>87.5</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>12.5</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>7.1</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1541,19 +1550,19 @@
       <c r="F29">
         <v>3</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>88.45999999999999</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>11.54</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>6.7</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1576,19 +1585,19 @@
       <c r="F30">
         <v>7</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>82.5</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>17.5</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>6.3</v>
       </c>
       <c r="J30">
         <v>7</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>17.5</v>
       </c>
     </row>
@@ -1611,19 +1620,19 @@
       <c r="F31">
         <v>10</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>77.27</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>22.73</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>7</v>
       </c>
       <c r="J31">
         <v>10</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>22.73</v>
       </c>
     </row>
@@ -1646,19 +1655,19 @@
       <c r="F32">
         <v>7</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>83.72</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>16.28</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>6.8</v>
       </c>
       <c r="J32">
         <v>7</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>16.28</v>
       </c>
     </row>
@@ -1681,19 +1690,19 @@
       <c r="F33">
         <v>8</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>61.9</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>38.1</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>6.7</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>33.33</v>
       </c>
     </row>
@@ -1716,19 +1725,19 @@
       <c r="F34">
         <v>7</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>79.41</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>20.59</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>8.1</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1742,42 +1751,45 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1800,19 +1812,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>80.56</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>19.44</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.4</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1835,19 +1847,19 @@
       <c r="F3">
         <v>6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>84.62</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>15.38</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1870,19 +1882,19 @@
       <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>72</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>28</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.7</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1905,19 +1917,19 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>77.78</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>22.22</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.4</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1940,19 +1952,19 @@
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>87.5</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12.5</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1975,19 +1987,19 @@
       <c r="F7">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>68.56999999999999</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>31.43</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2010,19 +2022,19 @@
       <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>78.56999999999999</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>21.43</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>21.43</v>
       </c>
     </row>
@@ -2045,19 +2057,19 @@
       <c r="F9">
         <v>22</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>33.33</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>66.67</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.9</v>
       </c>
       <c r="J9">
         <v>21</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>63.64</v>
       </c>
     </row>
@@ -2080,19 +2092,19 @@
       <c r="F10">
         <v>14</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>54.84</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>45.16</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J10">
         <v>13</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>41.94</v>
       </c>
     </row>
@@ -2115,19 +2127,19 @@
       <c r="F11">
         <v>11</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>47.62</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>52.38</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J11">
         <v>11</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>52.38</v>
       </c>
     </row>
@@ -2150,16 +2162,16 @@
       <c r="F12">
         <v>35</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>100</v>
       </c>
       <c r="J12">
         <v>35</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2182,19 +2194,19 @@
       <c r="F13">
         <v>11</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>47.62</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>52.38</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>8.1</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>42.86</v>
       </c>
     </row>
@@ -2217,16 +2229,16 @@
       <c r="F14">
         <v>31</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>100</v>
       </c>
       <c r="J14">
         <v>31</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2249,16 +2261,16 @@
       <c r="F15">
         <v>38</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
         <v>100</v>
       </c>
       <c r="J15">
         <v>38</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2281,16 +2293,16 @@
       <c r="F16">
         <v>35</v>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1">
         <v>100</v>
       </c>
       <c r="J16">
         <v>35</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2313,16 +2325,16 @@
       <c r="F17">
         <v>23</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
         <v>100</v>
       </c>
       <c r="J17">
         <v>23</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2345,16 +2357,16 @@
       <c r="F18">
         <v>32</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
         <v>100</v>
       </c>
       <c r="J18">
         <v>32</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2377,16 +2389,16 @@
       <c r="F19">
         <v>34</v>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="1">
         <v>100</v>
       </c>
       <c r="J19">
         <v>34</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2409,16 +2421,16 @@
       <c r="F20">
         <v>33</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
         <v>100</v>
       </c>
       <c r="J20">
         <v>33</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2441,19 +2453,19 @@
       <c r="F21">
         <v>4</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>81.81999999999999</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>18.18</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>8</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2476,19 +2488,19 @@
       <c r="F22">
         <v>8</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>78.95</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>21.05</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7.6</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2511,16 +2523,16 @@
       <c r="F23">
         <v>35</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1">
         <v>100</v>
       </c>
       <c r="J23">
         <v>35</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2543,16 +2555,16 @@
       <c r="F24">
         <v>31</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="1">
         <v>100</v>
       </c>
       <c r="J24">
         <v>31</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2575,16 +2587,16 @@
       <c r="F25">
         <v>36</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
         <v>100</v>
       </c>
       <c r="J25">
         <v>36</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2607,16 +2619,16 @@
       <c r="F26">
         <v>43</v>
       </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="1">
         <v>100</v>
       </c>
       <c r="J26">
         <v>43</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2639,16 +2651,16 @@
       <c r="F27">
         <v>43</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
         <v>100</v>
       </c>
       <c r="J27">
         <v>43</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2671,16 +2683,16 @@
       <c r="F28">
         <v>24</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1">
         <v>100</v>
       </c>
       <c r="J28">
         <v>24</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2703,16 +2715,16 @@
       <c r="F29">
         <v>26</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1">
         <v>100</v>
       </c>
       <c r="J29">
         <v>26</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2735,19 +2747,19 @@
       <c r="F30">
         <v>7</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>82.5</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>17.5</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>6.2</v>
       </c>
       <c r="J30">
         <v>7</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>17.5</v>
       </c>
     </row>
@@ -2770,19 +2782,19 @@
       <c r="F31">
         <v>10</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>77.27</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>22.73</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>6.9</v>
       </c>
       <c r="J31">
         <v>10</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>22.73</v>
       </c>
     </row>
@@ -2805,19 +2817,19 @@
       <c r="F32">
         <v>8</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>81.40000000000001</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>18.6</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>6.7</v>
       </c>
       <c r="J32">
         <v>8</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>18.6</v>
       </c>
     </row>
@@ -2840,19 +2852,19 @@
       <c r="F33">
         <v>8</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>61.9</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>38.1</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>6.7</v>
       </c>
       <c r="J33">
         <v>8</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>38.1</v>
       </c>
     </row>
@@ -2875,19 +2887,19 @@
       <c r="F34">
         <v>15</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>55.88</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>44.12</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>8.6</v>
       </c>
       <c r="J34">
         <v>15</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>44.12</v>
       </c>
     </row>
@@ -2901,42 +2913,45 @@
   <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2959,19 +2974,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>80.56</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>19.44</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7.2</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2994,19 +3009,19 @@
       <c r="F3">
         <v>6</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>84.62</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>15.38</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3029,19 +3044,19 @@
       <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>72</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>28</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3064,19 +3079,19 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>77.78</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>22.22</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3099,19 +3114,19 @@
       <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>87.5</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>12.5</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3134,19 +3149,19 @@
       <c r="F7">
         <v>11</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>68.56999999999999</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>31.43</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3169,19 +3184,19 @@
       <c r="F8">
         <v>6</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>78.56999999999999</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>21.43</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.3</v>
       </c>
       <c r="J8">
         <v>6</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>21.43</v>
       </c>
     </row>
@@ -3204,19 +3219,19 @@
       <c r="F9">
         <v>11</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>66.67</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>33.33</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>6.9</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>12.12</v>
       </c>
     </row>
@@ -3239,19 +3254,19 @@
       <c r="F10">
         <v>7</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>77.42</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>22.58</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8</v>
       </c>
       <c r="J10">
         <v>3</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>9.68</v>
       </c>
     </row>
@@ -3274,19 +3289,19 @@
       <c r="F11">
         <v>9</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>57.14</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>42.86</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.4</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>4.76</v>
       </c>
     </row>
@@ -3309,19 +3324,19 @@
       <c r="F12">
         <v>6</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>82.86</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>17.14</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3344,19 +3359,19 @@
       <c r="F13">
         <v>8</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>61.9</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>38.1</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>7.2</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>14.29</v>
       </c>
     </row>
@@ -3379,19 +3394,19 @@
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>96.77</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>3.23</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>8.5</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3414,19 +3429,19 @@
       <c r="F15">
         <v>12</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>68.42</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>31.58</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>9.1</v>
       </c>
       <c r="J15">
         <v>12</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>31.58</v>
       </c>
     </row>
@@ -3449,19 +3464,19 @@
       <c r="F16">
         <v>6</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>82.86</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>17.14</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J16">
         <v>6</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>17.14</v>
       </c>
     </row>
@@ -3484,19 +3499,19 @@
       <c r="F17">
         <v>2</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>91.3</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>8.699999999999999</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>9.5</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="1">
         <v>8.699999999999999</v>
       </c>
     </row>
@@ -3519,19 +3534,19 @@
       <c r="F18">
         <v>16</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>50</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>50</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J18">
         <v>16</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="1">
         <v>50</v>
       </c>
     </row>
@@ -3554,19 +3569,19 @@
       <c r="F19">
         <v>6</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>82.34999999999999</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>17.65</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>9.6</v>
       </c>
       <c r="J19">
         <v>6</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="1">
         <v>17.65</v>
       </c>
     </row>
@@ -3589,19 +3604,19 @@
       <c r="F20">
         <v>10</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>69.7</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>30.3</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>9</v>
       </c>
       <c r="J20">
         <v>10</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="1">
         <v>30.3</v>
       </c>
     </row>
@@ -3624,19 +3639,19 @@
       <c r="F21">
         <v>4</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>81.81999999999999</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>18.18</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3659,19 +3674,19 @@
       <c r="F22">
         <v>8</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>78.95</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>21.05</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3694,19 +3709,19 @@
       <c r="F23">
         <v>7</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>80</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>20</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>8.6</v>
       </c>
       <c r="J23">
         <v>7</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="1">
         <v>20</v>
       </c>
     </row>
@@ -3729,19 +3744,19 @@
       <c r="F24">
         <v>9</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>70.97</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>29.03</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>6.6</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3764,19 +3779,19 @@
       <c r="F25">
         <v>7</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>80.56</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>19.44</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>7.5</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3799,19 +3814,19 @@
       <c r="F26">
         <v>9</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>79.06999999999999</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>20.93</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>7.5</v>
       </c>
       <c r="J26">
         <v>2</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="1">
         <v>4.65</v>
       </c>
     </row>
@@ -3834,19 +3849,19 @@
       <c r="F27">
         <v>5</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>88.37</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>11.63</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>7.1</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3869,19 +3884,19 @@
       <c r="F28">
         <v>3</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>87.5</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>12.5</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>7.1</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3904,19 +3919,19 @@
       <c r="F29">
         <v>3</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>88.45999999999999</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>11.54</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>6.7</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3939,19 +3954,19 @@
       <c r="F30">
         <v>7</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>82.5</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>17.5</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>6.4</v>
       </c>
       <c r="J30">
         <v>7</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="1">
         <v>17.5</v>
       </c>
     </row>
@@ -3974,19 +3989,19 @@
       <c r="F31">
         <v>10</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>77.27</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>22.73</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>7.1</v>
       </c>
       <c r="J31">
         <v>10</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="1">
         <v>22.73</v>
       </c>
     </row>
@@ -4009,19 +4024,19 @@
       <c r="F32">
         <v>7</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>83.72</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>16.28</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>6.9</v>
       </c>
       <c r="J32">
         <v>7</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="1">
         <v>16.28</v>
       </c>
     </row>
@@ -4044,19 +4059,19 @@
       <c r="F33">
         <v>8</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="1">
         <v>61.9</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
         <v>38.1</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>6.9</v>
       </c>
       <c r="J33">
         <v>7</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="1">
         <v>33.33</v>
       </c>
     </row>
@@ -4079,19 +4094,19 @@
       <c r="F34">
         <v>7</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="1">
         <v>79.41</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
         <v>20.59</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>8.1</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Inglés - Estadisticos 20211.xlsx
+++ b/academias/Inglés - Estadisticos 20211.xlsx
@@ -185,7 +185,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Inglés - Estadisticos 20211.xlsx
+++ b/academias/Inglés - Estadisticos 20211.xlsx
@@ -1055,25 +1055,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
       <c r="I15" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K15" s="1">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1090,25 +1090,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="I16" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K16" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1160,25 +1160,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1">
-        <v>50</v>
+        <v>59.38</v>
       </c>
       <c r="H18" s="1">
-        <v>50</v>
+        <v>40.63</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K18" s="1">
-        <v>50</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1195,25 +1195,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>82.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H19" s="1">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
       <c r="I19" s="2">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1230,25 +1230,25 @@
         <v>33</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H20" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
       <c r="I20" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="J20">
         <v>9</v>
       </c>
-      <c r="J20">
-        <v>10</v>
-      </c>
       <c r="K20" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1440,25 +1440,25 @@
         <v>43</v>
       </c>
       <c r="E26">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1">
-        <v>79.06999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>20.93</v>
+        <v>18.6</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2122,25 +2122,25 @@
         <v>21</v>
       </c>
       <c r="E11">
+        <v>11</v>
+      </c>
+      <c r="F11">
         <v>10</v>
       </c>
-      <c r="F11">
-        <v>11</v>
-      </c>
       <c r="G11" s="1">
+        <v>52.38</v>
+      </c>
+      <c r="H11" s="1">
         <v>47.62</v>
       </c>
-      <c r="H11" s="1">
-        <v>52.38</v>
-      </c>
       <c r="I11" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K11" s="1">
-        <v>52.38</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2157,22 +2157,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>17.14</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2256,22 +2259,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>36.84</v>
+      </c>
+      <c r="I15" s="2">
+        <v>9.9</v>
       </c>
       <c r="J15">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2288,22 +2294,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>82.86</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>17.14</v>
+      </c>
+      <c r="I16" s="2">
+        <v>9.800000000000001</v>
       </c>
       <c r="J16">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>17.14</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2320,22 +2329,25 @@
         <v>23</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F17">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>73.91</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>26.09</v>
+      </c>
+      <c r="I17" s="2">
+        <v>9.6</v>
       </c>
       <c r="J17">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2352,22 +2364,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>50</v>
+      </c>
+      <c r="I18" s="2">
+        <v>9.4</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2384,22 +2399,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>94.12</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>5.88</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J19">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2416,22 +2434,25 @@
         <v>33</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F20">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>60.61</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>39.39</v>
+      </c>
+      <c r="I20" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J20">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>39.39</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2550,22 +2571,25 @@
         <v>31</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I24" s="2">
+        <v>6.5</v>
       </c>
       <c r="J24">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2582,22 +2606,25 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I25" s="2">
+        <v>7.5</v>
       </c>
       <c r="J25">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2614,22 +2641,25 @@
         <v>43</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F26">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>20.93</v>
+      </c>
+      <c r="I26" s="2">
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2646,22 +2676,25 @@
         <v>43</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F27">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>100</v>
+        <v>18.6</v>
+      </c>
+      <c r="I27" s="2">
+        <v>6.9</v>
       </c>
       <c r="J27">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K27" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2678,22 +2711,25 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H28" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I28" s="2">
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K28" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2710,22 +2746,25 @@
         <v>26</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1">
-        <v>0</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="H29" s="1">
-        <v>100</v>
+        <v>11.54</v>
+      </c>
+      <c r="I29" s="2">
+        <v>7.1</v>
       </c>
       <c r="J29">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K29" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3296,7 +3335,7 @@
         <v>42.86</v>
       </c>
       <c r="I11" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -3319,19 +3358,19 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3424,25 +3463,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>68.42</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
       <c r="I15" s="2">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K15" s="1">
-        <v>31.58</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3459,25 +3498,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="I16" s="2">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K16" s="1">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3506,7 +3545,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I17" s="2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -3529,25 +3568,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1">
-        <v>50</v>
+        <v>59.38</v>
       </c>
       <c r="H18" s="1">
-        <v>50</v>
+        <v>40.63</v>
       </c>
       <c r="I18" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J18">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K18" s="1">
-        <v>50</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3564,25 +3603,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>82.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H19" s="1">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
       <c r="I19" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>17.65</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3599,25 +3638,25 @@
         <v>33</v>
       </c>
       <c r="E20">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="1">
-        <v>69.7</v>
+        <v>72.73</v>
       </c>
       <c r="H20" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
       <c r="I20" s="2">
         <v>9</v>
       </c>
       <c r="J20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K20" s="1">
-        <v>30.3</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3739,16 +3778,16 @@
         <v>31</v>
       </c>
       <c r="E24">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G24" s="1">
-        <v>70.97</v>
+        <v>64.52</v>
       </c>
       <c r="H24" s="1">
-        <v>29.03</v>
+        <v>35.48</v>
       </c>
       <c r="I24" s="2">
         <v>6.6</v>
@@ -3774,19 +3813,19 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1">
-        <v>80.56</v>
+        <v>69.44</v>
       </c>
       <c r="H25" s="1">
-        <v>19.44</v>
+        <v>30.56</v>
       </c>
       <c r="I25" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3821,13 +3860,13 @@
         <v>20.93</v>
       </c>
       <c r="I26" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>4.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3844,19 +3883,19 @@
         <v>43</v>
       </c>
       <c r="E27">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>88.37</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H27" s="1">
-        <v>11.63</v>
+        <v>18.6</v>
       </c>
       <c r="I27" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3879,16 +3918,16 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="H28" s="1">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="I28" s="2">
         <v>7.1</v>
@@ -3926,7 +3965,7 @@
         <v>11.54</v>
       </c>
       <c r="I29" s="2">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20211.xlsx
+++ b/academias/Inglés - Estadisticos 20211.xlsx
@@ -1335,25 +1335,25 @@
         <v>35</v>
       </c>
       <c r="E23">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="H23" s="1">
-        <v>20</v>
+        <v>17.14</v>
       </c>
       <c r="I23" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>20</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2227,22 +2227,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>96.77</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>3.23</v>
+      </c>
+      <c r="I14" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2539,22 +2542,25 @@
         <v>35</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>14.29</v>
+      </c>
+      <c r="I23" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J23">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3440,7 +3446,7 @@
         <v>3.23</v>
       </c>
       <c r="I14" s="2">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3743,25 +3749,25 @@
         <v>35</v>
       </c>
       <c r="E23">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>80</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>20</v>
+        <v>14.29</v>
       </c>
       <c r="I23" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>20</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="24" spans="1:11">

--- a/academias/Inglés - Estadisticos 20211.xlsx
+++ b/academias/Inglés - Estadisticos 20211.xlsx
@@ -810,25 +810,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>78.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>21.43</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>21.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -845,25 +845,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>66.67</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>33.33</v>
+        <v>21.21</v>
       </c>
       <c r="I9" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -880,25 +880,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>77.42</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>22.58</v>
+        <v>12.9</v>
       </c>
       <c r="I10" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -915,25 +915,25 @@
         <v>21</v>
       </c>
       <c r="E11">
+        <v>11</v>
+      </c>
+      <c r="F11">
         <v>10</v>
       </c>
-      <c r="F11">
-        <v>11</v>
-      </c>
       <c r="G11" s="1">
+        <v>52.38</v>
+      </c>
+      <c r="H11" s="1">
         <v>47.62</v>
       </c>
-      <c r="H11" s="1">
-        <v>52.38</v>
-      </c>
       <c r="I11" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -985,25 +985,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F13">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H13" s="1">
-        <v>42.86</v>
+        <v>28.57</v>
       </c>
       <c r="I13" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1055,25 +1055,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>73.68000000000001</v>
+        <v>97.37</v>
       </c>
       <c r="H15" s="1">
-        <v>26.32</v>
+        <v>2.63</v>
       </c>
       <c r="I15" s="2">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1090,25 +1090,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1125,25 +1125,25 @@
         <v>23</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1160,25 +1160,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>59.38</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>40.63</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>40.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1195,25 +1195,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1230,25 +1230,25 @@
         <v>33</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>72.73</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1347,13 +1347,13 @@
         <v>17.14</v>
       </c>
       <c r="I23" s="2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1580,25 +1580,25 @@
         <v>40</v>
       </c>
       <c r="E30">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1615,25 +1615,25 @@
         <v>44</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H31" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1650,25 +1650,25 @@
         <v>43</v>
       </c>
       <c r="E32">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>83.72</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1685,25 +1685,25 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>61.9</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>38.1</v>
+        <v>4.76</v>
       </c>
       <c r="I33" s="2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2017,25 +2017,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>78.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>21.43</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>21.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2052,25 +2052,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>33.33</v>
+        <v>96.97</v>
       </c>
       <c r="H9" s="1">
-        <v>66.67</v>
+        <v>3.03</v>
       </c>
       <c r="I9" s="2">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="J9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>63.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2087,25 +2087,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>54.84</v>
+        <v>96.77</v>
       </c>
       <c r="H10" s="1">
-        <v>45.16</v>
+        <v>3.23</v>
       </c>
       <c r="I10" s="2">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>41.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2122,25 +2122,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>47.62</v>
+        <v>4.76</v>
       </c>
       <c r="I11" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2157,25 +2157,25 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>82.86</v>
+        <v>97.14</v>
       </c>
       <c r="H12" s="1">
-        <v>17.14</v>
+        <v>2.86</v>
       </c>
       <c r="I12" s="2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2192,25 +2192,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>47.62</v>
+        <v>90.48</v>
       </c>
       <c r="H13" s="1">
-        <v>52.38</v>
+        <v>9.52</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2262,25 +2262,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>63.16</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>36.84</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>36.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2297,25 +2297,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>82.86</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>17.14</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>17.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2332,25 +2332,25 @@
         <v>23</v>
       </c>
       <c r="E17">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>73.91</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>26.09</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>26.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2367,25 +2367,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>9.4</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2402,25 +2402,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2437,25 +2437,25 @@
         <v>33</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>60.61</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2542,25 +2542,25 @@
         <v>35</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>14.29</v>
+        <v>11.43</v>
       </c>
       <c r="I23" s="2">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2787,25 +2787,25 @@
         <v>40</v>
       </c>
       <c r="E30">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
         <v>6.2</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2822,25 +2822,25 @@
         <v>44</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H31" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2857,25 +2857,25 @@
         <v>43</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F32">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J32">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>18.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2892,25 +2892,25 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>61.9</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H33" s="1">
-        <v>38.1</v>
+        <v>4.76</v>
       </c>
       <c r="I33" s="2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="J33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2927,25 +2927,25 @@
         <v>34</v>
       </c>
       <c r="E34">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1">
-        <v>55.88</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H34" s="1">
-        <v>44.12</v>
+        <v>11.76</v>
       </c>
       <c r="I34" s="2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J34">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K34" s="1">
-        <v>44.12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3014,19 +3014,19 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
-        <v>80.56</v>
+        <v>66.67</v>
       </c>
       <c r="H2" s="1">
-        <v>19.44</v>
+        <v>33.33</v>
       </c>
       <c r="I2" s="2">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -3049,19 +3049,19 @@
         <v>39</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" s="1">
-        <v>84.62</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>15.38</v>
+        <v>12.82</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -3084,19 +3084,19 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H4" s="1">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>22.22</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -3154,19 +3154,19 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1">
-        <v>87.5</v>
+        <v>81.25</v>
       </c>
       <c r="H6" s="1">
-        <v>12.5</v>
+        <v>18.75</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -3189,19 +3189,19 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>68.56999999999999</v>
+        <v>77.14</v>
       </c>
       <c r="H7" s="1">
-        <v>31.43</v>
+        <v>22.86</v>
       </c>
       <c r="I7" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3224,25 +3224,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>78.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>21.43</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="J8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>21.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -3259,25 +3259,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
         <v>6.9</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -3294,25 +3294,25 @@
         <v>31</v>
       </c>
       <c r="E10">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>77.42</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>22.58</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -3329,25 +3329,25 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>57.14</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>42.86</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -3364,19 +3364,19 @@
         <v>35</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3399,25 +3399,25 @@
         <v>21</v>
       </c>
       <c r="E13">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -3434,19 +3434,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -3469,25 +3469,25 @@
         <v>38</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>73.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -3504,25 +3504,25 @@
         <v>35</v>
       </c>
       <c r="E16">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -3539,25 +3539,25 @@
         <v>23</v>
       </c>
       <c r="E17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -3574,25 +3574,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>59.38</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>40.63</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>40.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -3609,25 +3609,25 @@
         <v>34</v>
       </c>
       <c r="E19">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>97.06</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -3644,25 +3644,25 @@
         <v>33</v>
       </c>
       <c r="E20">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>72.73</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="J20">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>27.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -3679,19 +3679,19 @@
         <v>22</v>
       </c>
       <c r="E21">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>81.81999999999999</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>18.18</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -3714,16 +3714,16 @@
         <v>38</v>
       </c>
       <c r="E22">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F22">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>78.95</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
         <v>7.9</v>
@@ -3749,25 +3749,25 @@
         <v>35</v>
       </c>
       <c r="E23">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -3784,19 +3784,19 @@
         <v>31</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G24" s="1">
-        <v>64.52</v>
+        <v>83.87</v>
       </c>
       <c r="H24" s="1">
-        <v>35.48</v>
+        <v>16.13</v>
       </c>
       <c r="I24" s="2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -3819,16 +3819,16 @@
         <v>36</v>
       </c>
       <c r="E25">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1">
-        <v>69.44</v>
+        <v>94.44</v>
       </c>
       <c r="H25" s="1">
-        <v>30.56</v>
+        <v>5.56</v>
       </c>
       <c r="I25" s="2">
         <v>7.6</v>
@@ -3854,19 +3854,19 @@
         <v>43</v>
       </c>
       <c r="E26">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F26">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G26" s="1">
-        <v>79.06999999999999</v>
+        <v>86.05</v>
       </c>
       <c r="H26" s="1">
-        <v>20.93</v>
+        <v>13.95</v>
       </c>
       <c r="I26" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3889,19 +3889,19 @@
         <v>43</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G27" s="1">
-        <v>81.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="H27" s="1">
-        <v>18.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I27" s="2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -3924,19 +3924,19 @@
         <v>24</v>
       </c>
       <c r="E28">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="I28" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -3959,19 +3959,19 @@
         <v>26</v>
       </c>
       <c r="E29">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>88.45999999999999</v>
+        <v>100</v>
       </c>
       <c r="H29" s="1">
-        <v>11.54</v>
+        <v>0</v>
       </c>
       <c r="I29" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -3994,25 +3994,25 @@
         <v>40</v>
       </c>
       <c r="E30">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="H30" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="I30" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J30">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -4029,25 +4029,25 @@
         <v>44</v>
       </c>
       <c r="E31">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>77.27</v>
+        <v>100</v>
       </c>
       <c r="H31" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
       <c r="I31" s="2">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -4064,25 +4064,25 @@
         <v>43</v>
       </c>
       <c r="E32">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>83.72</v>
+        <v>100</v>
       </c>
       <c r="H32" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J32">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -4099,25 +4099,25 @@
         <v>21</v>
       </c>
       <c r="E33">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F33">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="H33" s="1">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J33">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K33" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -4134,19 +4134,19 @@
         <v>34</v>
       </c>
       <c r="E34">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G34" s="1">
-        <v>79.41</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H34" s="1">
-        <v>20.59</v>
+        <v>8.82</v>
       </c>
       <c r="I34" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J34">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20211.xlsx
+++ b/academias/Inglés - Estadisticos 20211.xlsx
@@ -3329,19 +3329,19 @@
         <v>21</v>
       </c>
       <c r="E11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
         <v>0</v>
